--- a/项目/净收入比例录入/专户产品KPI净收入数据拆分及确认流程需求20260303_修订20260908.xlsx
+++ b/项目/净收入比例录入/专户产品KPI净收入数据拆分及确认流程需求20260303_修订20260908.xlsx
@@ -12,6 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策定稿" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待确认清单" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勘误记录" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入数据清单" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="处理规则" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="122211" fullCalcOnLoad="1"/>
@@ -909,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1339,6 +1341,125 @@
       <c r="C25" s="14" t="inlineStr">
         <is>
           <t>界面展示柜台管理费/总管理费占比作为参考值，银行部显式设置生效值</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Q29</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>直销的分行维度</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>销量表承载直销产品各地区销量分布（直销部分拆分公司依据）；管理费表柜台渠道仅用于计算混合产品的直销总占比；勘误E1撤销</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Q30</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>总部份额与规则链融合</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>直销/代销/混合三规则＝剩余份额（1−总部份额）在分公司间的分配算法；总部份额仍由银行部每月设置（参考值＝柜台占比）；勘误E2修订</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Q31</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>地区口径统一</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>销量表"分行"与管理费表"名称（地名）"统一归一为"地区"，经地区→分公司映射落到分公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Q32</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>量纲差异</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>直销内部占比用销量、代销内部占比用管理费，维持现状口径，不设统一计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Q33</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>新输入定位</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>分公司代码、地区对应规则＝系统主数据（银行业务部维护）；产品信息表由产品系统接口同步（转待确认C5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Q34</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>专户数据更新表结构</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>属性列（专户类型、基金募集类型、产品类型、建行/行外、条线、业务/管理部门等，经产品信息表下拉）＋净收入（总）＋各主体拆分列纳入导出需求；合计列固定、明细列自动计算（业务/管理部门区别转待确认C6）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Q35</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>混合产品识别</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>按管理费表两销售商并存动态判断，不维护封闭产品清单（当前如536392、536744）</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1467,6 +1588,50 @@
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>产品信息表与产品系统的接口同步方案</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>金融科技部/产品系统团队</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>"业务部门"与"管理部门"的区别及口径</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>创新发展部</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
@@ -1483,7 +1648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1533,17 +1698,17 @@
       </c>
       <c r="C2" s="14" t="inlineStr">
         <is>
-          <t>输入表《直销产品销量情况（01）》挂在直销分支</t>
+          <t>（原勘误）输入表《直销产品销量情况（01）》挂在直销分支，分行数据属代销拆分</t>
         </is>
       </c>
       <c r="D2" s="14" t="inlineStr">
         <is>
-          <t>该表分行数据属代销拆分数据源</t>
+          <t>【20260909撤销】销量表未挂错：直销部分按分行（地区）销量占比拆分（Q29）</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
         <is>
-          <t>直销＝柜台不经分行，分行属代销</t>
+          <t>原勘误有误，予以撤销</t>
         </is>
       </c>
     </row>
@@ -1560,17 +1725,17 @@
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>直销总占比×直销内占比＋代销总占比×代销内占比</t>
+          <t>（原勘误）公式作废，替换为"总部份额＋剩余按分行数据自动分配"</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>总部份额（银行部设置）＋剩余按分行数据自动分配</t>
+          <t>【20260909修订】公式保留，作为剩余份额（1−总部份额）在分公司间的分配算法（Q30）</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>直销内分公司占比无数据来源；详见ADR 0001</t>
+          <t>与总部份额模型融合，见ADR 0001</t>
         </is>
       </c>
     </row>
@@ -1652,6 +1817,417 @@
       <c r="E6" s="14" t="inlineStr">
         <is>
           <t>术语统一；结果不再上传able</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>xmind 代销输入字段</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>渠道名称</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>销售商名称（建设银行＝代销、建信直销＝直销）＋名称（地区名）</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>管理费表实际字段口径（20260909补充）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>关键字段</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>频率/时点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>直销产品销量情况</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>银行业务部（周晓彤）邮件</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>产品代码、产品名称、分行（地区）、销量</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>每月初（或上月末）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>建行一对多专户产品区间管理费</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>able-大数据-数据查询系统-通用报表展示-专户理财部；起始＝上月初第一天、结束＝上月末最后一天</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>基金代码、基金名称、销售商名称（建设银行/建信直销）、名称（地区名）、总管理费</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>每月</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>专户净收入表</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>计划财务部（陈佳禾）上传；月初第2个工作日从able-报表服务系统-通用报表-KPI净收入拆分（专户）导出上月</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>开始月份、产品、产品名称、总净收入</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>每月</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>分公司代码</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>系统主数据（银行业务部维护）</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>分公司、代码</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>分公司地区对应规则</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>系统主数据（银行业务部维护）</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>地区、分公司名称</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>产品信息表</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>产品系统（接口同步，转待确认C5）</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>全量专户产品信息（专户类型、基金募集类型、产品类型、建行/行外、条线、业务/管理部门等）</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>同步</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>环节</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>定位</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>直销</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>取销量表产品代码、分行、销量，按产品分组计算组内各地区销量占比</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>剩余份额分配算法·直销链</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>代销</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>管理费表筛选销售商名称＝建设银行，名称拆分保留地名，按产品分组计算组内各地区管理费占比</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>剩余份额分配算法·代销链</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>混合产品</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>动态识别两销售商并存的产品（当前如536392、536744）；直销总占比＝建信直销柜台管理费/总管理费，代销总占比＝其余/总管理费；地区占比＝直销总占比×直销内地区占比＋代销总占比×代销内地区占比</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>剩余份额分配算法·混合链</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>专户数据更新</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>合计列产品数据不动，明细列写入各产品地区占比；属性列（专户类型、基金募集类型、产品类型、建行/行外、条线、业务/管理部门等）经产品信息表公式下拉</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>输出表加工</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>净收入匹配与拆分</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>净收入表（③）匹配到专户数据更新的净收入（总）；净收入拆分＝收入占比×净收入（总）；与able源sheet对比，缺少的产品补入</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>计算与缺数补全（Q13）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>总部份额</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>银行部每月设置总部份额（界面展示柜台占比参考值，不自动采用）；R1-R3算得的地区占比×（1−总部份额）分配至分公司</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>目标系统模型（Q30融合，ADR 0001）</t>
         </is>
       </c>
     </row>
